--- a/local/templates/competitionBook/BestLifter.xlsx
+++ b/local/templates/competitionBook/BestLifter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/Misc/usaw-owlcms/local/templates/competitionBook/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Library/Application Support/owlcms/64.0.2+quick-start/local/templates/competitionBook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF57EB8-AB56-FA40-B750-D733BCBB1D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEA9481-7F18-7949-880B-C37C5C4F7DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18040" yWindow="1240" windowWidth="39500" windowHeight="25100" xr2:uid="{C695CBD2-3DAD-B341-8FFD-602D797EB14F}"/>
+    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" xr2:uid="{C695CBD2-3DAD-B341-8FFD-602D797EB14F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -371,9 +371,6 @@
     <t>${athlete.total == 0 ? "DNF" : athlete.bestLifterScore}</t>
   </si>
   <si>
-    <t>${mBest.0.ageGroup.championshipName} - Best Lifter</t>
-  </si>
-  <si>
     <t>Women</t>
   </si>
   <si>
@@ -387,6 +384,9 @@
   </si>
   <si>
     <t>${athlete.team}</t>
+  </si>
+  <si>
+    <t>${mBest.0.ageGroup.championshipName} - Best Lifters</t>
   </si>
 </sst>
 </file>
@@ -949,7 +949,7 @@
     </row>
     <row r="2" spans="1:16" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -987,7 +987,7 @@
     </row>
     <row r="4" spans="1:16" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -1048,7 +1048,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -1059,7 +1059,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>15</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="10" spans="1:16" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -1143,7 +1143,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1154,7 +1154,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>15</v>

--- a/local/templates/competitionBook/BestLifter.xlsx
+++ b/local/templates/competitionBook/BestLifter.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Library/Application Support/owlcms/64.0.2+quick-start/local/templates/competitionBook/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/templates/competitionBook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEA9481-7F18-7949-880B-C37C5C4F7DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D42F29-53FF-574B-A521-275D5DB6371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" xr2:uid="{C695CBD2-3DAD-B341-8FFD-602D797EB14F}"/>
   </bookViews>
@@ -386,14 +386,14 @@
     <t>${athlete.team}</t>
   </si>
   <si>
-    <t>${mBest.0.ageGroup.championshipName} - Best Lifters</t>
+    <t>${ageGroupPrefix ? ageGroupPrefix : championship ? championship.name : ""}${championship ? " - " : ""}Best Lifters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -440,6 +440,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -531,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -577,6 +585,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -948,17 +959,17 @@
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>

--- a/local/templates/competitionBook/BestLifter.xlsx
+++ b/local/templates/competitionBook/BestLifter.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/templates/competitionBook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D42F29-53FF-574B-A521-275D5DB6371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B07D8B-6324-BE48-B73B-D1DE903AC3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" xr2:uid="{C695CBD2-3DAD-B341-8FFD-602D797EB14F}"/>
   </bookViews>
@@ -50,7 +50,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:area(lastCell="I14")</t>
+          <t>jx:area(lastCell="J14")</t>
         </r>
       </text>
     </comment>
@@ -63,7 +63,58 @@
             <rFont val="Tahoma"/>
             <family val="34"/>
           </rPr>
-          <t>jx:each(</t>
+          <t xml:space="preserve">jx:each(
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="34"/>
+          </rPr>
+          <t xml:space="preserve">  items="wBest"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="34"/>
+          </rPr>
+          <t xml:space="preserve">  var="athlete"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="34"/>
+          </rPr>
+          <t xml:space="preserve">  varIndex="athleteIndex"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="34"/>
+          </rPr>
+          <t xml:space="preserve">  lastCell="J8"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="34"/>
+          </rPr>
+          <t xml:space="preserve">)
+</t>
         </r>
         <r>
           <rPr>
@@ -82,84 +133,6 @@
             <rFont val="Tahoma"/>
             <family val="34"/>
           </rPr>
-          <t xml:space="preserve">  items="wBest"</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">  var="athlete"
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">  varIndex="athleteIndex"
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">  lastCell="I8"</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="34"/>
-          </rPr>
           <t xml:space="preserve">jx:if(
 </t>
         </r>
@@ -180,7 +153,7 @@
             <rFont val="Tahoma"/>
             <family val="34"/>
           </rPr>
-          <t xml:space="preserve">  lastCell="I8"
+          <t xml:space="preserve">  lastCell="J8"
 </t>
         </r>
         <r>
@@ -243,7 +216,7 @@
             <rFont val="Tahoma"/>
             <family val="34"/>
           </rPr>
-          <t xml:space="preserve">  lastCell="I14"
+          <t xml:space="preserve">  lastCell="J14"
 </t>
         </r>
         <r>
@@ -293,7 +266,7 @@
             <rFont val="Tahoma"/>
             <family val="34"/>
           </rPr>
-          <t xml:space="preserve">  lastCell="I14"
+          <t xml:space="preserve">  lastCell="J14"
 </t>
         </r>
         <r>
@@ -312,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>${competition.competitionName}</t>
   </si>
@@ -387,6 +360,12 @@
   </si>
   <si>
     <t>${ageGroupPrefix ? ageGroupPrefix : championship ? championship.name : ""}${championship ? " - " : ""}Best Lifters</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>${athlete.bestLifterRank == -1 ? "ext" : athlete.bestLifterRank}</t>
   </si>
 </sst>
 </file>
@@ -539,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -589,6 +568,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -927,18 +912,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="6.83203125" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" customWidth="1"/>
-    <col min="6" max="8" width="6.83203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" customWidth="1"/>
+    <col min="7" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -950,15 +936,16 @@
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
       <c r="I1" s="16"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="18"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
     </row>
-    <row r="2" spans="1:16" ht="19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>24</v>
       </c>
@@ -970,15 +957,16 @@
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="19"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
     </row>
-    <row r="3" spans="1:16" ht="19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -988,15 +976,16 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="10"/>
+      <c r="J3" s="1"/>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
     </row>
-    <row r="4" spans="1:16" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>19</v>
       </c>
@@ -1008,90 +997,98 @@
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="14"/>
       <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>20</v>
       </c>
@@ -1103,97 +1100,105 @@
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="69" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
